--- a/artfynd/A 17398-2023 artfynd.xlsx
+++ b/artfynd/A 17398-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126185213</v>
       </c>
       <c r="B2" t="n">
-        <v>98259</v>
+        <v>98261</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 17398-2023 artfynd.xlsx
+++ b/artfynd/A 17398-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126185213</v>
       </c>
       <c r="B2" t="n">
-        <v>98261</v>
+        <v>98263</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 17398-2023 artfynd.xlsx
+++ b/artfynd/A 17398-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126185213</v>
       </c>
       <c r="B2" t="n">
-        <v>98263</v>
+        <v>98265</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 17398-2023 artfynd.xlsx
+++ b/artfynd/A 17398-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126185213</v>
       </c>
       <c r="B2" t="n">
-        <v>98265</v>
+        <v>98269</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 17398-2023 artfynd.xlsx
+++ b/artfynd/A 17398-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126185213</v>
       </c>
       <c r="B2" t="n">
-        <v>98269</v>
+        <v>98272</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 17398-2023 artfynd.xlsx
+++ b/artfynd/A 17398-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126185213</v>
       </c>
       <c r="B2" t="n">
-        <v>98272</v>
+        <v>98281</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
